--- a/results/Int Task Remove ACC -0.7/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_2_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6839687288366345</v>
+        <v>0.7127386878538864</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6817415573444296</v>
+        <v>0.7135738771634632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6897562329384002</v>
+        <v>0.6901330717512271</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.690172693062256</v>
+        <v>0.6887060063813002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6894076701272769</v>
+        <v>0.6810116175967493</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.686132541139837</v>
+        <v>0.679692070850584</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6909750682463991</v>
+        <v>0.6687995266387863</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7070304263741788</v>
+        <v>0.6606117041701867</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7001452199593663</v>
+        <v>0.6609251837940111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7001452199593663</v>
+        <v>0.6620738527274124</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7052684125643192</v>
+        <v>0.6654847763403173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7031000621373864</v>
+        <v>0.6473731245330969</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6433170891776221</v>
+        <v>0.6835681521458343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6449874677967758</v>
+        <v>0.6854795749523497</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6444306749237246</v>
+        <v>0.6784053382298525</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6327188248354056</v>
+        <v>0.5894008629416816</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6362067220085037</v>
+        <v>0.5862660667034371</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6405230013055834</v>
+        <v>0.6011818321452758</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6398960420579344</v>
+        <v>0.5992330570895965</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6421254826120044</v>
+        <v>0.5857183500778462</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6346789452004105</v>
+        <v>0.5809131752204482</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6508350147663564</v>
+        <v>0.5659544721463929</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6494034112726994</v>
+        <v>0.5887988633745489</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6446401267881953</v>
+        <v>0.6182477955191265</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6533779349442509</v>
+        <v>0.5795733814607174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6443379924736963</v>
+        <v>0.5768527762844635</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6406837556115645</v>
+        <v>0.577166255908288</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.622973902297687</v>
+        <v>0.6088978642891553</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6462506370827544</v>
+        <v>0.6284196507739246</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6462506370827544</v>
+        <v>0.5972912637627329</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6343893779977798</v>
+        <v>0.5686481976667062</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6283042777052453</v>
+        <v>0.5864859911611313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6233587700986518</v>
+        <v>0.5493086343040263</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.63124777457394</v>
+        <v>0.5466955477515343</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6323964435073413</v>
+        <v>0.5071801844572753</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6375456430521326</v>
+        <v>0.524208795581962</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6277949605881408</v>
+        <v>0.5025074879041548</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6261902102198547</v>
+        <v>0.5480367378570281</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6048589341692789</v>
+        <v>0.5826779817218339</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6067024596630618</v>
+        <v>0.5694484783322046</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.580318157382131</v>
+        <v>0.6079588217634451</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5987274053801201</v>
+        <v>0.6061152962696623</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6107776947727797</v>
+        <v>0.6067422555173112</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.578828780082524</v>
+        <v>0.6212438298971591</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6245955833583512</v>
+        <v>0.6332850430423582</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6256740859171548</v>
+        <v>0.634082880102771</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6164225970634849</v>
+        <v>0.6342560269774001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6164225970634849</v>
+        <v>0.6229684914578548</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6106022788362855</v>
+        <v>0.6258577053850074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6065338509121629</v>
+        <v>0.5989110248479729</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6056635784152873</v>
+        <v>0.6010238705308208</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6059419748518129</v>
+        <v>0.5872602648867913</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5921183263399683</v>
+        <v>0.574910110241498</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6216079270548973</v>
+        <v>0.6002068337161648</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6831267323414624</v>
+        <v>0.6154111191013119</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6819407111588972</v>
+        <v>0.5893425655060706</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5713869553378808</v>
+        <v>0.6114365954297603</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.551574379847938</v>
+        <v>0.6109103476202777</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5497591303558588</v>
+        <v>0.6097220573758475</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5372471741452618</v>
+        <v>0.6118134342425872</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5074802242531296</v>
+        <v>0.6004738848433649</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5084557463119017</v>
+        <v>0.5837814439611536</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5104067904294461</v>
+        <v>0.5569241295529599</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5110032046135264</v>
+        <v>0.5569241295529599</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5299240387904853</v>
+        <v>0.5569241295529599</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5405268412564319</v>
+        <v>0.5704931195062521</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5573754983208943</v>
+        <v>0.5828104600261117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5776282718126662</v>
+        <v>0.5821393413437036</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5724349128331156</v>
+        <v>0.5910876486235521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6248741543380971</v>
+        <v>0.5787374939782589</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5951934287968387</v>
+        <v>0.5633532545328874</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6083515440093276</v>
+        <v>0.5887880416948845</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6137440568033457</v>
+        <v>0.5887880416948845</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6377585857810111</v>
+        <v>0.584719613770762</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6296896272454985</v>
+        <v>0.5906666503759661</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5700087620696637</v>
+        <v>0.591293609623615</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5877865126962738</v>
+        <v>0.591293609623615</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6265571000691191</v>
+        <v>0.6444978740635756</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6390872087746368</v>
+        <v>0.5676344506426682</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6346328657902269</v>
+        <v>0.5573337824912205</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6459485027682554</v>
+        <v>0.5183322744377963</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4867228463112036</v>
+        <v>0.5099430290928639</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4860517276287954</v>
+        <v>0.5101863423420907</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.499821093199098</v>
+        <v>0.4990222088793627</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4941287151524461</v>
+        <v>0.4995790017524139</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4940257346524146</v>
+        <v>0.4998924813762384</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4940257346524146</v>
+        <v>0.5006575043112176</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4981711361367301</v>
+        <v>0.5010411503096397</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4988172951386222</v>
+        <v>0.4992327080031557</v>
       </c>
     </row>
   </sheetData>
